--- a/C题/p1/result1.xlsx
+++ b/C题/p1/result1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>911.16</v>
+        <v>577.83</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>569.36</v>
+        <v>902.6900000000001</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>904.95</v>
+        <v>571.62</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="B145" s="7" t="n">
-        <v>0</v>
+        <v>907.45</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +1984,7 @@
         <v>833.33</v>
       </c>
       <c r="C3" t="n">
-        <v>6365.84</v>
+        <v>5947.42</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4787.96</v>
+        <v>3954.63</v>
       </c>
       <c r="C4" t="n">
-        <v>1703</v>
+        <v>2121.42</v>
       </c>
     </row>
     <row r="5" ht="14" customFormat="1" customHeight="1" s="5">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5286.04</v>
+        <v>6119.37</v>
       </c>
       <c r="C5" t="n">
         <v>91.09999999999999</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5780.13</v>
+        <v>5068.69</v>
       </c>
     </row>
     <row r="7" ht="14" customFormat="1" customHeight="1" s="5">
@@ -2044,7 +2044,7 @@
         <v>5333.33</v>
       </c>
       <c r="C7" t="n">
-        <v>3433.99</v>
+        <v>3571.31</v>
       </c>
     </row>
   </sheetData>
